--- a/teacher_forms/024_student_council_nomination_form--teacher_forms.xlsx
+++ b/teacher_forms/024_student_council_nomination_form--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>student_council_nominations</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Student Nominations</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,59 +548,59 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>name_title</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Role of Interest</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>position_id</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Available to Serve</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>name_title</t>
+          <t>skills</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Skills and Strengths</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>student_council_nominations</t>
+          <t>availability</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Student Nominations</t>
+          <t>Availability</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>name_title</t>
+          <t>position_id</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Position Desires</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,40 +699,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>position_id</t>
+          <t>student_council_nominations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Student Council Nominations</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>name_title</t>
+          <t>student_council_committee</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Student Council Committee</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>student_council_nominations</t>
+          <t>school_events</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Student Nominations</t>
+          <t>School Events</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>extracurricular_activities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Extracurricular Activities</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>name_title</t>
+          <t>student_leadership</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Student Leadership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>position_id</t>
+          <t>class_representative</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Class Representative</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>student_council_nominations</t>
+          <t>position_ideas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Student Nominations</t>
+          <t>Position Ideas</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Name Title</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>position_id</t>
+          <t>position_id_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -921,52 +921,6 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>student_council_nominations</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Student Nominations</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -983,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1011,119 +965,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>student_council_nominations_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>president</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>President</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>student_council_nominations_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>vice_president</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Vice President</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>student_council_nominations_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>secretary</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Secretary</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>student_council_nominations_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>treasurer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Treasurer</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>student_council_nominations_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>student_council_nominations_choices</t>
+          <t>available_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>student_council_nominations_choices</t>
+          <t>available_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1106,182 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>student_council_nominations_choices</t>
+          <t>student_council_committee_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>student_council_committee_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>school_events_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>school_events_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>extracurricular_activities_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>extracurricular_activities_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>student_leadership_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>student_leadership_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>class_representative_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>class_representative_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
